--- a/data/trans_dic/P29A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,63; 58,66</t>
+          <t>49,64; 58,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,38; 63,03</t>
+          <t>53,74; 63,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,27; 63,56</t>
+          <t>53,8; 63,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,55; 50,67</t>
+          <t>34,24; 51,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,54; 41,51</t>
+          <t>31,86; 40,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,32; 44,14</t>
+          <t>34,4; 44,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,43; 45,86</t>
+          <t>36,53; 46,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,07; 39,38</t>
+          <t>24,94; 39,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,36; 48,8</t>
+          <t>42,63; 48,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,37; 52,02</t>
+          <t>45,61; 52,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,84; 53,87</t>
+          <t>46,54; 53,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,53; 44,0</t>
+          <t>32,96; 44,1</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,43; 69,05</t>
+          <t>61,61; 68,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,69; 67,22</t>
+          <t>59,87; 67,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,64; 64,01</t>
+          <t>55,68; 63,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,94; 60,0</t>
+          <t>48,6; 60,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,13; 36,94</t>
+          <t>29,18; 36,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,18; 34,79</t>
+          <t>27,36; 35,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,27; 42,98</t>
+          <t>34,92; 43,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,49; 33,77</t>
+          <t>17,54; 34,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,73; 53,2</t>
+          <t>47,49; 52,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,84; 50,55</t>
+          <t>44,73; 50,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,57; 52,45</t>
+          <t>46,89; 52,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,15; 44,54</t>
+          <t>29,69; 45,22</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,05; 64,15</t>
+          <t>55,67; 63,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,64; 63,34</t>
+          <t>55,81; 63,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,94; 66,89</t>
+          <t>59,4; 67,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,24; 56,77</t>
+          <t>48,03; 56,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,94; 33,73</t>
+          <t>26,91; 34,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,49; 32,7</t>
+          <t>25,66; 32,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,05; 39,86</t>
+          <t>32,35; 39,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,74; 31,0</t>
+          <t>24,71; 30,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,2; 47,18</t>
+          <t>41,75; 47,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41,21; 46,66</t>
+          <t>41,33; 46,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,14; 52,19</t>
+          <t>46,69; 52,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,46; 43,22</t>
+          <t>37,51; 43,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,98; 62,63</t>
+          <t>53,69; 62,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,66; 64,9</t>
+          <t>56,35; 65,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,06; 63,25</t>
+          <t>54,95; 62,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 55,55</t>
+          <t>18,73; 54,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,9; 29,44</t>
+          <t>21,26; 29,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,26; 35,26</t>
+          <t>27,11; 35,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,4; 42,47</t>
+          <t>34,57; 42,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 30,02</t>
+          <t>22,26; 30,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,68; 44,98</t>
+          <t>39,38; 45,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42,37; 49,03</t>
+          <t>42,79; 49,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,96; 51,74</t>
+          <t>45,81; 51,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,78; 40,6</t>
+          <t>19,95; 40,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,18; 49,66</t>
+          <t>39,34; 49,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,51; 55,86</t>
+          <t>44,63; 55,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,07; 62,31</t>
+          <t>53,02; 62,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,98; 50,91</t>
+          <t>43,41; 51,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,51; 21,13</t>
+          <t>13,56; 21,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 25,86</t>
+          <t>17,57; 26,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,95; 29,42</t>
+          <t>21,05; 30,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,94; 27,29</t>
+          <t>21,99; 27,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 34,04</t>
+          <t>27,28; 33,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,06; 38,67</t>
+          <t>32,15; 39,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,67; 44,27</t>
+          <t>37,84; 44,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,68; 39,07</t>
+          <t>33,68; 38,64</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,25; 48,21</t>
+          <t>37,22; 48,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,68; 53,42</t>
+          <t>40,71; 52,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,34; 56,6</t>
+          <t>45,6; 56,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,19; 56,32</t>
+          <t>47,57; 56,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,23</t>
+          <t>5,38; 11,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 16,67</t>
+          <t>9,16; 16,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,2; 21,59</t>
+          <t>13,4; 21,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,73; 77,51</t>
+          <t>17,91; 78,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,62; 27,45</t>
+          <t>20,51; 27,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,1; 32,18</t>
+          <t>24,62; 32,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,15; 36,34</t>
+          <t>29,13; 36,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,76; 76,24</t>
+          <t>33,69; 74,04</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,51; 40,24</t>
+          <t>27,53; 40,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,9; 39,65</t>
+          <t>26,04; 39,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,05; 41,21</t>
+          <t>29,85; 41,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,65; 39,71</t>
+          <t>30,97; 39,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,4</t>
+          <t>2,64; 7,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,92</t>
+          <t>3,23; 7,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,69</t>
+          <t>4,95; 11,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,4</t>
+          <t>4,96; 8,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,68; 19,28</t>
+          <t>12,82; 19,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,18</t>
+          <t>12,73; 19,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,26; 21,56</t>
+          <t>15,54; 21,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,86; 20,48</t>
+          <t>15,79; 20,28</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,24; 56,61</t>
+          <t>52,95; 56,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>54,36; 58,09</t>
+          <t>54,31; 58,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55,41; 58,82</t>
+          <t>55,34; 58,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,17; 49,79</t>
+          <t>34,76; 49,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,05; 25,95</t>
+          <t>23,1; 26,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,28; 27,35</t>
+          <t>24,29; 27,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,24; 32,44</t>
+          <t>29,13; 32,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,31; 40,2</t>
+          <t>23,29; 41,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,67</t>
+          <t>38,25; 40,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39,29; 41,71</t>
+          <t>39,16; 41,7</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42,34; 44,85</t>
+          <t>42,4; 44,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,43; 42,68</t>
+          <t>33,1; 42,22</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>242747; 286902</t>
+          <t>242797; 286717</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>235033; 277515</t>
+          <t>236615; 278866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216121; 257868</t>
+          <t>218266; 257647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134189; 202688</t>
+          <t>136960; 207277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>151167; 192814</t>
+          <t>148004; 188128</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>146297; 188160</t>
+          <t>146651; 188756</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>142814; 179778</t>
+          <t>143173; 181353</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78515; 123353</t>
+          <t>78120; 123409</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>403913; 465406</t>
+          <t>406553; 464851</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>393116; 450784</t>
+          <t>395226; 454241</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>373618; 429711</t>
+          <t>371283; 429425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>231975; 313811</t>
+          <t>235074; 314505</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>443805; 498873</t>
+          <t>445132; 498039</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>390230; 439459</t>
+          <t>391401; 441090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>321318; 369664</t>
+          <t>321543; 365761</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>203035; 254142</t>
+          <t>205863; 255629</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>181902; 230660</t>
+          <t>182194; 229973</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>162271; 207728</t>
+          <t>163347; 212523</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>195988; 238812</t>
+          <t>194024; 239506</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89313; 172415</t>
+          <t>89548; 176236</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>642961; 716600</t>
+          <t>639642; 712969</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>560803; 632258</t>
+          <t>559477; 632956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>527736; 594322</t>
+          <t>531325; 597032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>281636; 416113</t>
+          <t>277314; 422419</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>353935; 405127</t>
+          <t>351524; 403189</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>363079; 413292</t>
+          <t>364149; 416371</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>382388; 434015</t>
+          <t>385402; 435291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>258676; 304363</t>
+          <t>257528; 304408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>183813; 230144</t>
+          <t>183631; 232919</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>175700; 225371</t>
+          <t>176845; 227121</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>208483; 259334</t>
+          <t>210455; 256673</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>133826; 167718</t>
+          <t>133670; 167495</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541252; 619811</t>
+          <t>548551; 623742</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>552915; 626072</t>
+          <t>554459; 627914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>612594; 678189</t>
+          <t>606712; 677115</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>403557; 465544</t>
+          <t>404064; 465955</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>276543; 320845</t>
+          <t>275062; 320640</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>329393; 377238</t>
+          <t>327543; 378234</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>345562; 396952</t>
+          <t>344847; 394613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157400; 490811</t>
+          <t>165470; 485849</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>111737; 150249</t>
+          <t>108498; 148696</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>163842; 211961</t>
+          <t>162939; 215163</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>217470; 268494</t>
+          <t>218549; 265779</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>161989; 213746</t>
+          <t>158478; 213751</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>395523; 460006</t>
+          <t>402709; 465347</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>500942; 579690</t>
+          <t>506004; 579985</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>579003; 651764</t>
+          <t>577123; 649002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>299719; 647740</t>
+          <t>318281; 653228</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>149191; 189091</t>
+          <t>149802; 186954</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>185894; 228188</t>
+          <t>182316; 226053</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>241767; 283827</t>
+          <t>241513; 284889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240780; 285212</t>
+          <t>243187; 287823</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>54461; 85138</t>
+          <t>54655; 84828</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76385; 113072</t>
+          <t>76841; 114558</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>101843; 143032</t>
+          <t>102320; 146139</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>119299; 148430</t>
+          <t>119573; 149822</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>214317; 266798</t>
+          <t>213806; 266253</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>271167; 327055</t>
+          <t>271952; 330153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>354714; 416877</t>
+          <t>356348; 419356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>371879; 431401</t>
+          <t>371793; 426652</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>107387; 138970</t>
+          <t>107291; 139957</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119910; 157468</t>
+          <t>119996; 154675</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146269; 182569</t>
+          <t>147103; 182258</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>173341; 206868</t>
+          <t>174710; 206538</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18883; 38517</t>
+          <t>18434; 38553</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31650; 57915</t>
+          <t>31835; 57373</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49622; 81182</t>
+          <t>50383; 80241</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>107776; 471068</t>
+          <t>108830; 478548</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>130128; 173263</t>
+          <t>129431; 170693</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>154728; 206639</t>
+          <t>158079; 205927</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>203640; 253871</t>
+          <t>203534; 253505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>329138; 743419</t>
+          <t>328466; 721912</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57275; 83771</t>
+          <t>57302; 84964</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>65501; 96544</t>
+          <t>63400; 95332</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75054; 102933</t>
+          <t>74561; 103131</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86553; 112119</t>
+          <t>87432; 112884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8792; 24617</t>
+          <t>8771; 25884</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12940; 30731</t>
+          <t>12513; 30197</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19796; 46239</t>
+          <t>19581; 44809</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21076; 35613</t>
+          <t>21040; 35429</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>68590; 104310</t>
+          <t>69366; 104489</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81345; 121101</t>
+          <t>80352; 121077</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98462; 139091</t>
+          <t>100257; 139581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>112035; 144612</t>
+          <t>111488; 143231</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1721081; 1830050</t>
+          <t>1711533; 1832417</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1779918; 1902363</t>
+          <t>1778373; 1900727</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1821769; 1933711</t>
+          <t>1819409; 1934282</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1248887; 1719386</t>
+          <t>1200308; 1723251</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>774438; 871859</t>
+          <t>776264; 875351</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>846381; 953364</t>
+          <t>846842; 949519</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1019800; 1131476</t>
+          <t>1016079; 1129875</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>851493; 1468125</t>
+          <t>850746; 1518369</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2521204; 2681089</t>
+          <t>2521776; 2683702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2656385; 2820098</t>
+          <t>2647611; 2819507</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2868467; 3039082</t>
+          <t>2873027; 3037583</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2375497; 3032422</t>
+          <t>2351846; 3000156</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P29A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,64; 58,62</t>
+          <t>49,42; 58,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,74; 63,34</t>
+          <t>53,36; 62,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,8; 63,5</t>
+          <t>53,28; 63,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,24; 51,82</t>
+          <t>33,96; 49,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,86; 40,5</t>
+          <t>32,08; 41,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,4; 44,28</t>
+          <t>34,32; 43,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 46,27</t>
+          <t>36,39; 46,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,94; 39,4</t>
+          <t>24,37; 37,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,63; 48,75</t>
+          <t>42,44; 48,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,61; 52,42</t>
+          <t>45,29; 52,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,54; 53,83</t>
+          <t>46,59; 53,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,96; 44,1</t>
+          <t>30,96; 40,96</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,61; 68,93</t>
+          <t>61,78; 69,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,87; 67,47</t>
+          <t>59,82; 67,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,68; 63,34</t>
+          <t>55,47; 63,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,6; 60,35</t>
+          <t>46,09; 58,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,18; 36,83</t>
+          <t>29,2; 37,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,36; 35,6</t>
+          <t>27,01; 34,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,92; 43,1</t>
+          <t>35,23; 43,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,54; 34,52</t>
+          <t>26,46; 34,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,49; 52,93</t>
+          <t>47,45; 53,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,73; 50,61</t>
+          <t>44,97; 50,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,89; 52,69</t>
+          <t>46,88; 52,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,69; 45,22</t>
+          <t>37,3; 44,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,67; 63,85</t>
+          <t>55,62; 63,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,81; 63,81</t>
+          <t>55,81; 63,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,4; 67,09</t>
+          <t>59,25; 66,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,03; 56,77</t>
+          <t>46,28; 54,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,91; 34,14</t>
+          <t>26,96; 33,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,66; 32,96</t>
+          <t>25,42; 32,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,35; 39,45</t>
+          <t>32,07; 39,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,71; 30,96</t>
+          <t>24,27; 30,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,75; 47,48</t>
+          <t>41,55; 47,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41,33; 46,8</t>
+          <t>41,08; 46,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,69; 52,11</t>
+          <t>46,67; 52,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,51; 43,26</t>
+          <t>36,2; 41,64</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,69; 62,59</t>
+          <t>54,25; 63,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,35; 65,07</t>
+          <t>56,46; 65,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,95; 62,88</t>
+          <t>54,85; 62,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 54,99</t>
+          <t>47,09; 54,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,26; 29,14</t>
+          <t>21,79; 29,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,11; 35,79</t>
+          <t>26,92; 35,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,57; 42,04</t>
+          <t>34,69; 42,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,26; 30,02</t>
+          <t>26,33; 31,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,38; 45,51</t>
+          <t>38,92; 45,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42,79; 49,05</t>
+          <t>42,55; 48,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,81; 51,52</t>
+          <t>45,7; 51,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,95; 40,94</t>
+          <t>37,18; 42,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,34; 49,1</t>
+          <t>39,48; 49,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,63; 55,34</t>
+          <t>44,87; 55,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,02; 62,54</t>
+          <t>52,44; 62,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,41; 51,38</t>
+          <t>42,85; 50,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 21,05</t>
+          <t>13,64; 21,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 26,2</t>
+          <t>17,87; 26,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 30,06</t>
+          <t>20,98; 29,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,99; 27,55</t>
+          <t>21,37; 26,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,28; 33,97</t>
+          <t>27,43; 33,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,15; 39,04</t>
+          <t>32,32; 38,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,84; 44,53</t>
+          <t>37,72; 44,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,68; 38,64</t>
+          <t>32,73; 37,77</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,22; 48,55</t>
+          <t>36,58; 47,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,71; 52,47</t>
+          <t>40,69; 53,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,6; 56,5</t>
+          <t>45,57; 56,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,57; 56,23</t>
+          <t>47,25; 55,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,24</t>
+          <t>5,42; 11,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 16,52</t>
+          <t>8,91; 16,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,4; 21,34</t>
+          <t>13,51; 21,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,91; 78,74</t>
+          <t>15,98; 21,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,51; 27,04</t>
+          <t>20,43; 27,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,62; 32,07</t>
+          <t>24,7; 32,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,13; 36,29</t>
+          <t>29,25; 36,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,69; 74,04</t>
+          <t>31,72; 36,96</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,53; 40,82</t>
+          <t>26,86; 39,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,04; 39,15</t>
+          <t>25,95; 39,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,85; 41,29</t>
+          <t>29,58; 41,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,97; 39,98</t>
+          <t>30,6; 40,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,78</t>
+          <t>2,54; 7,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,79</t>
+          <t>3,04; 7,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,33</t>
+          <t>5,01; 11,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,36</t>
+          <t>5,14; 8,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,82; 19,32</t>
+          <t>12,88; 18,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 19,18</t>
+          <t>12,83; 19,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,54; 21,63</t>
+          <t>15,52; 21,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,28</t>
+          <t>16,03; 20,41</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,95; 56,69</t>
+          <t>53,22; 56,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>54,31; 58,04</t>
+          <t>54,21; 57,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55,34; 58,84</t>
+          <t>55,33; 58,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34,76; 49,91</t>
+          <t>45,81; 49,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,1; 26,05</t>
+          <t>22,97; 25,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,24</t>
+          <t>24,27; 27,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,13; 32,39</t>
+          <t>29,16; 32,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,29; 41,57</t>
+          <t>23,07; 25,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,25; 40,71</t>
+          <t>38,1; 40,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39,16; 41,7</t>
+          <t>39,14; 41,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42,4; 44,83</t>
+          <t>42,29; 44,75</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,22</t>
+          <t>34,4; 36,83</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279083</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>242797; 286717</t>
+          <t>241690; 284971</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>236615; 278866</t>
+          <t>234941; 276208</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>218266; 257647</t>
+          <t>216190; 259079</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136960; 207277</t>
+          <t>138477; 200980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>148004; 188128</t>
+          <t>149022; 191575</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>146651; 188756</t>
+          <t>146305; 186702</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>143173; 181353</t>
+          <t>142636; 180556</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78120; 123409</t>
+          <t>88356; 137311</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>406553; 464851</t>
+          <t>404730; 465581</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>395226; 454241</t>
+          <t>392435; 451903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>371283; 429425</t>
+          <t>371632; 426347</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>235074; 314505</t>
+          <t>238513; 315502</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>445132; 498039</t>
+          <t>446338; 498877</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>391401; 441090</t>
+          <t>391033; 440631</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>321543; 365761</t>
+          <t>320330; 367949</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205863; 255629</t>
+          <t>219816; 277212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>182194; 229973</t>
+          <t>182347; 231459</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>163347; 212523</t>
+          <t>161245; 205758</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>194024; 239506</t>
+          <t>195793; 241348</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89548; 176236</t>
+          <t>132346; 174853</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>639642; 712969</t>
+          <t>639097; 714884</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>559477; 632956</t>
+          <t>562519; 632662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>531325; 597032</t>
+          <t>531272; 597615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>277314; 422419</t>
+          <t>364411; 435316</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282184</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>351524; 403189</t>
+          <t>351213; 401781</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>364149; 416371</t>
+          <t>364177; 416884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>385402; 435291</t>
+          <t>384407; 432780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257528; 304408</t>
+          <t>286794; 340212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>183631; 232919</t>
+          <t>183979; 231215</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>176845; 227121</t>
+          <t>175213; 225697</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>210455; 256673</t>
+          <t>208663; 259688</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>133670; 167495</t>
+          <t>150613; 190108</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>548551; 623742</t>
+          <t>545851; 622219</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>554459; 627914</t>
+          <t>551175; 627718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>606712; 677115</t>
+          <t>606486; 678189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>404064; 465955</t>
+          <t>448986; 516468</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>344267</t>
+          <t>354936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>192392</t>
+          <t>212010</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>536659</t>
+          <t>566946</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>275062; 320640</t>
+          <t>277940; 322873</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>327543; 378234</t>
+          <t>328211; 379399</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344847; 394613</t>
+          <t>344225; 394381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165470; 485849</t>
+          <t>327875; 379244</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>108498; 148696</t>
+          <t>111179; 150527</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>162939; 215163</t>
+          <t>161832; 210915</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>218549; 265779</t>
+          <t>219275; 267281</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>158478; 213751</t>
+          <t>193619; 230720</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>402709; 465347</t>
+          <t>397975; 460589</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>506004; 579985</t>
+          <t>503090; 576931</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>577123; 649002</t>
+          <t>575758; 647813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>318281; 653228</t>
+          <t>532300; 602544</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264194</t>
+          <t>281793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>134297</t>
+          <t>147527</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>398490</t>
+          <t>429319</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>149802; 186954</t>
+          <t>150337; 189175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>182316; 226053</t>
+          <t>183296; 224968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>241513; 284889</t>
+          <t>238880; 285391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>243187; 287823</t>
+          <t>260643; 304235</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>54655; 84828</t>
+          <t>54963; 85394</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76841; 114558</t>
+          <t>78142; 114849</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>102320; 146139</t>
+          <t>102001; 143060</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>119573; 149822</t>
+          <t>129568; 162661</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>213806; 266253</t>
+          <t>214994; 261516</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>271952; 330153</t>
+          <t>273367; 329154</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>356348; 419356</t>
+          <t>355156; 419877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>371793; 426652</t>
+          <t>397545; 458806</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>470149</t>
+          <t>288688</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>107291; 139957</t>
+          <t>105442; 138353</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119996; 154675</t>
+          <t>119942; 156410</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>147103; 182258</t>
+          <t>147000; 182596</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>174710; 206538</t>
+          <t>191928; 224612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18434; 38553</t>
+          <t>18604; 37948</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31835; 57373</t>
+          <t>30958; 57403</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50383; 80241</t>
+          <t>50806; 81445</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>108830; 478548</t>
+          <t>70061; 92312</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>129431; 170693</t>
+          <t>128940; 171727</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>158079; 205927</t>
+          <t>158582; 206525</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>203534; 253505</t>
+          <t>204315; 254185</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>328466; 721912</t>
+          <t>267953; 312162</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99624</t>
+          <t>109317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>127058</t>
+          <t>140850</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57302; 84964</t>
+          <t>55911; 82929</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63400; 95332</t>
+          <t>63196; 95025</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74561; 103131</t>
+          <t>73883; 102466</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87432; 112884</t>
+          <t>94797; 124420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8771; 25884</t>
+          <t>8442; 25377</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12513; 30197</t>
+          <t>11806; 30435</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19581; 44809</t>
+          <t>19826; 45752</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21040; 35429</t>
+          <t>23783; 41313</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>69366; 104489</t>
+          <t>69685; 102136</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80352; 121077</t>
+          <t>81023; 122405</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>100257; 139581</t>
+          <t>100155; 141816</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>111488; 143231</t>
+          <t>123733; 157587</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1580302</t>
+          <t>1682411</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1028192</t>
+          <t>907649</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2608494</t>
+          <t>2590061</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1711533; 1832417</t>
+          <t>1720474; 1832180</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1778373; 1900727</t>
+          <t>1775043; 1894175</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1819409; 1934282</t>
+          <t>1819001; 1933753</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1200308; 1723251</t>
+          <t>1614562; 1751951</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>776264; 875351</t>
+          <t>771836; 872284</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>846842; 949519</t>
+          <t>846100; 953775</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1016079; 1129875</t>
+          <t>1017218; 1127265</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>850746; 1518369</t>
+          <t>859504; 958057</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2521776; 2683702</t>
+          <t>2512024; 2675544</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2647611; 2819507</t>
+          <t>2645986; 2819861</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2873027; 3037583</t>
+          <t>2865621; 3032254</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2351846; 3000156</t>
+          <t>2494475; 2670491</t>
         </is>
       </c>
     </row>
